--- a/Pruebas/Archivos/Template/Ecuador/Template_HRC_MICO.xlsx
+++ b/Pruebas/Archivos/Template/Ecuador/Template_HRC_MICO.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
